--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-03).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-03).xlsx
@@ -935,10 +935,10 @@
     <t>214</t>
   </si>
   <si>
-    <t>23</t>
+    <t>22</t>
   </si>
   <si>
-    <t>R$ 4.558,40</t>
+    <t>R$ 4.554,43</t>
   </si>
   <si>
     <t>50.0</t>
@@ -959,7 +959,7 @@
     <t>6.4</t>
   </si>
   <si>
-    <t>43.2%</t>
+    <t>43.3%</t>
   </si>
   <si>
     <t>17.9%</t>
@@ -10169,7 +10169,7 @@
         <v>19618</v>
       </c>
       <c r="B58" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C58" s="4">
         <v>51</v>
@@ -10199,18 +10199,30 @@
         <v>58</v>
       </c>
       <c r="L58" s="4"/>
-      <c r="M58" s="5"/>
-      <c r="N58" s="6"/>
+      <c r="M58" s="5">
+        <v>3796.98</v>
+      </c>
+      <c r="N58" s="6">
+        <v>43</v>
+      </c>
       <c r="O58" s="6">
         <v>30</v>
       </c>
-      <c r="P58" s="7"/>
-      <c r="Q58" s="8"/>
-      <c r="R58" s="8"/>
+      <c r="P58" s="7">
+        <v>4.5898365853658536</v>
+      </c>
+      <c r="Q58" s="8">
+        <v>20.693333333333332</v>
+      </c>
+      <c r="R58" s="8">
+        <v>8.4355566666666668</v>
+      </c>
       <c r="S58" s="8">
         <v>7</v>
       </c>
-      <c r="T58" s="9"/>
+      <c r="T58" s="9">
+        <v>0.20000000000000001</v>
+      </c>
       <c r="U58" s="9">
         <v>0.066666666666666666</v>
       </c>

--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-03).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-03).xlsx
@@ -935,19 +935,19 @@
     <t>214</t>
   </si>
   <si>
-    <t>22</t>
+    <t>18</t>
   </si>
   <si>
-    <t>R$ 4.554,43</t>
+    <t>R$ 4.529,19</t>
   </si>
   <si>
-    <t>50.0</t>
+    <t>49.7</t>
   </si>
   <si>
     <t>31.6</t>
   </si>
   <si>
-    <t>5.02</t>
+    <t>5.01</t>
   </si>
   <si>
     <t>18.4</t>
@@ -959,7 +959,7 @@
     <t>6.4</t>
   </si>
   <si>
-    <t>43.3%</t>
+    <t>43.9%</t>
   </si>
   <si>
     <t>17.9%</t>
@@ -5019,7 +5019,7 @@
         <v>19536</v>
       </c>
       <c r="B24" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C24" s="4">
         <v>51</v>
@@ -5049,14 +5049,26 @@
         <v>58</v>
       </c>
       <c r="L24" s="4"/>
-      <c r="M24" s="5"/>
-      <c r="N24" s="6"/>
+      <c r="M24" s="5">
+        <v>3958.27</v>
+      </c>
+      <c r="N24" s="6">
+        <v>43</v>
+      </c>
       <c r="O24" s="6"/>
-      <c r="P24" s="7"/>
-      <c r="Q24" s="8"/>
-      <c r="R24" s="8"/>
+      <c r="P24" s="7">
+        <v>4.7515880952380956</v>
+      </c>
+      <c r="Q24" s="8">
+        <v>28.358559459459457</v>
+      </c>
+      <c r="R24" s="8">
+        <v>16.653602702702702</v>
+      </c>
       <c r="S24" s="8"/>
-      <c r="T24" s="9"/>
+      <c r="T24" s="9">
+        <v>0.10810810810810811</v>
+      </c>
       <c r="U24" s="9"/>
       <c r="V24" s="9"/>
       <c r="W24" s="9"/>
@@ -6843,7 +6855,7 @@
         <v>19562</v>
       </c>
       <c r="B36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C36" s="4">
         <v>51</v>
@@ -6873,14 +6885,26 @@
         <v>58</v>
       </c>
       <c r="L36" s="4"/>
-      <c r="M36" s="5"/>
-      <c r="N36" s="6"/>
+      <c r="M36" s="5">
+        <v>4297.6999999999998</v>
+      </c>
+      <c r="N36" s="6">
+        <v>60</v>
+      </c>
       <c r="O36" s="6"/>
-      <c r="P36" s="7"/>
-      <c r="Q36" s="8"/>
-      <c r="R36" s="8"/>
+      <c r="P36" s="7">
+        <v>5.4755741379310345</v>
+      </c>
+      <c r="Q36" s="8">
+        <v>17.626515909090909</v>
+      </c>
+      <c r="R36" s="8">
+        <v>5.6139534883720934</v>
+      </c>
       <c r="S36" s="8"/>
-      <c r="T36" s="9"/>
+      <c r="T36" s="9">
+        <v>0.52272727272727271</v>
+      </c>
       <c r="U36" s="9"/>
       <c r="V36" s="9"/>
       <c r="W36" s="9"/>
@@ -9132,7 +9156,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>51</v>
@@ -9162,14 +9186,26 @@
         <v>58</v>
       </c>
       <c r="L51" s="4"/>
-      <c r="M51" s="5"/>
-      <c r="N51" s="6"/>
+      <c r="M51" s="5">
+        <v>425.19999999999999</v>
+      </c>
+      <c r="N51" s="6">
+        <v>4</v>
+      </c>
       <c r="O51" s="6"/>
-      <c r="P51" s="7"/>
-      <c r="Q51" s="8"/>
-      <c r="R51" s="8"/>
+      <c r="P51" s="7">
+        <v>2.9375</v>
+      </c>
+      <c r="Q51" s="8">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="R51" s="8">
+        <v>6.0833000000000004</v>
+      </c>
       <c r="S51" s="8"/>
-      <c r="T51" s="9"/>
+      <c r="T51" s="9">
+        <v>0</v>
+      </c>
       <c r="U51" s="9"/>
       <c r="V51" s="9"/>
       <c r="W51" s="9"/>
@@ -14834,7 +14870,7 @@
         <v>19693</v>
       </c>
       <c r="B89" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C89" s="4">
         <v>51</v>
@@ -14862,14 +14898,26 @@
         <v>58</v>
       </c>
       <c r="L89" s="4"/>
-      <c r="M89" s="5"/>
-      <c r="N89" s="6"/>
+      <c r="M89" s="5">
+        <v>4588.4399999999996</v>
+      </c>
+      <c r="N89" s="6">
+        <v>44</v>
+      </c>
       <c r="O89" s="6"/>
-      <c r="P89" s="7"/>
-      <c r="Q89" s="8"/>
-      <c r="R89" s="8"/>
+      <c r="P89" s="7">
+        <v>4.6311586956521742</v>
+      </c>
+      <c r="Q89" s="8">
+        <v>19.995677777777775</v>
+      </c>
+      <c r="R89" s="8">
+        <v>6.8025653846153853</v>
+      </c>
       <c r="S89" s="8"/>
-      <c r="T89" s="9"/>
+      <c r="T89" s="9">
+        <v>0.25925925925925924</v>
+      </c>
       <c r="U89" s="9"/>
       <c r="V89" s="9"/>
       <c r="W89" s="9"/>
